--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_10_Data Pipeline _ Observability/Day_10_FULL_TOAN_BO_64_CAU.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_10_Data Pipeline _ Observability/Day_10_FULL_TOAN_BO_64_CAU.xlsx
@@ -1350,7 +1350,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I18" s="4" t="n">
@@ -1359,7 +1359,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Assume lần đầu có thể đã ghi một phần, nên replay phải không nhân bản.</t>
+          <t>Khi trang P7 bị timeout sau khi server có thể đã xử lý nhưng client chưa nhận được phản hồi xác nhận: (a) Lưu lại định danh/cursor của P7 kèm số lần thử và thông tin lỗi; (b) Giữ nguyên checkpoint tại trang thành công trước đó (P6); (c) Khi thực hiện replay trang P7 phải sử dụng mã định danh ổn định của từng bản ghi để đảm bảo tính idempotent (không nhân bản dữ liệu nếu server đã ghi một phần). Không được nhảy cóc sang P8.</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,5</t>
         </is>
       </c>
       <c r="I20" s="4" t="n">
@@ -1456,7 +1456,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: OCR quality không chỉ là một scalar confidence.</t>
+          <t>Các dấu hiệu cảnh báo chất lượng OCR kém cần cách ly (quarantine) để người xem xét trước khi đưa vào embedding: (a) Điểm độ tin cậy thấp (0,42) và xuất hiện nhiều ký tự thay thế lỗi; (b) Ngôn ngữ văn bản bị thay đổi bất thường (từ tiếng Việt sang tiếng Nga); (c) Chiều dài văn bản giảm đột ngột 95% so với các trang tương tự; (e) Bảng dữ liệu bị mất các cột dù số lượng từ ngữ vẫn đủ.</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1501,7 +1501,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính chênh rate rồi nhân thời gian.</t>
+          <t>Tốc độ chênh lệch giữa producer và consumer là: 120 event/s - 90 event/s = 30 event/s. Trong khoảng thời gian 60 giây không co giãn (no scaling), độ sâu hàng đợi (queue depth) tăng thêm là: 30 event/s × 60 s = 1800 event.</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4 → o5</t>
+          <t>o2 → o3 → o4 → o5 → o1</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1598,7 +1598,7 @@
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Không replay trước khi biết nguyên nhân vẫn tồn tại.</t>
+          <t>Trình tự xử lý thông điệp độc hại (poison message workflow) với Dead-Letter Queue (DLQ): 1. Consumer tiếp nhận và xử lý message (o2) -&gt; 2. Thử lại có giới hạn (bounded retries) theo điều kiện eligibility (o3) -&gt; 3. Đưa failed event kèm lý do vi phạm và run ID vào DLQ để không chặn nghẽn hàng đợi (o4) -&gt; 4. Kỹ sư kiểm tra, tạo ticket và khắc phục nguyên nhân gốc (o5) -&gt; 5. Replay có chủ đích các message trong DLQ sau khi đã sửa lỗi (o1).</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I26" s="4" t="n">
@@ -1740,7 +1740,7 @@
       <c r="J26" s="3" t="n"/>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một người khác phải rerun mà không hỏi người sửa.</t>
+          <t>Một quy trình làm sạch dữ liệu được chứng minh là có thể tái lập (replayable) khi thỏa mãn: (a) Dữ liệu thô ban đầu và phiên bản của nó được lưu trữ bất biến; (b) Toàn bộ các quy tắc làm sạch nằm trong mã nguồn và hợp đồng dữ liệu có quản lý phiên bản; (c) Cùng một dữ liệu đầu vào và bộ quy tắc luôn tạo ra cùng một kết quả xác định; (d) Có dấu vết lineage ghi nhận đầy đủ trạng thái trước và sau khi xử lý của từng lần chạy.</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I33" s="4" t="n">
@@ -2101,7 +2101,7 @@
       <c r="J33" s="3" t="n"/>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Reviewer phải biết record nào, từ đâu, vì sao và làm tiếp gì.</t>
+          <t>Một bản ghi trong vùng cách ly (quarantine entry) cần lưu giữ đầy đủ để có thể khắc phục hoặc phục vụ kiểm toán: (a) Dòng dữ liệu gốc hoặc tham chiếu bất biến tới dữ liệu gốc; (b) Quy tắc/lý do vi phạm và bằng chứng lỗi cụ thể; (c) Định danh nguồn và mã định danh lần chạy (Run ID); (d) Người chịu trách nhiệm xem xét, trạng thái xử lý và quyết định replay.</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="J34" s="3" t="n"/>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dùng số phân vùng dự kiến làm mẫu số.</t>
+          <t>Độ bao phủ phân vùng (partition coverage) được tính bằng tỷ lệ phần trăm giữa số phân vùng thực tế xuất hiện trên tổng số phân vùng dự kiến: 228 / 240 = 19 / 20 = 0,95 = 95%.</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       <c r="G35" s="3" t="n"/>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I35" s="4" t="n">
@@ -2194,7 +2194,7 @@
       <c r="J35" s="3" t="n"/>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ chấm rule được cung cấp.</t>
+          <t>Đối chiếu bản ghi `{age: 150, email: 'a@b', status: 'active'}` với schema đã cho: (a) Trường age=150 nằm ngoài khoảng cho phép 0..120 nên không hợp lệ; (b) Trường email='a@b' có chứa ký tự '@' nên hợp lệ theo đúng quy tắc kiểm tra đã nêu; (c) Trường status='active' thuộc tập hợp giá trị hợp lệ {active, inactive} nên hợp lệ.</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I37" s="4" t="n">
@@ -2291,7 +2291,7 @@
       <c r="J37" s="3" t="n"/>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Consistency hỏi các phần liên quan có đồng ý theo invariant không.</t>
+          <t>Các phép kiểm tra tính nhất quán (consistency checks) trong bộ dữ liệu orders gồm: (a) Tính nhất quán trong bản ghi: `order.total = sum(line.amount)` cùng đơn vị tiền tệ; (b) Tính nhất quán tham chiếu: mọi `customer_id` đều tham chiếu tới một khách hàng tồn tại trong bảng customers; (c) Tính nhất quán giữa các biểu diễn: cùng một order_id phải có cùng trạng thái trên các view tại cùng một thời điểm. Kiểm tra email chứa @ và order.total nằm trong dải là các kiểm tra hợp lệ định dạng/miền giá trị (validity), không phải consistency.</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -2336,7 +2336,7 @@
       <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Clock dừng ở publish boundary, không ở job start.</t>
+          <t>Độ trễ dữ liệu (freshness lag) được tính từ thời điểm phát sinh sự kiện nguồn (09:00) đến ranh giới xuất bản phục vụ người dùng (09:18): 09:18 - 09:00 = 18 phút. Độ trễ 18 phút đã vượt quá mức SLA tối đa 15 phút là 3 phút.</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I40" s="4" t="n">
@@ -2433,7 +2433,7 @@
       <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một operator phải biết check gì và làm gì khi fail.</t>
+          <t>Một hợp đồng dữ liệu (data contract) có tính thực thi cao cho validator và operator cần: (a) Định nghĩa schema chuẩn hóa, các trường bắt buộc, miền giá trị và khóa định danh; (b) Xác định rõ người sở hữu (owner) và nguồn sự thật có thẩm quyền; (c) Quy định mức độ nghiêm trọng và hậu quả xử lý cho từng loại vi phạm; (d) Khi độ mới dữ liệu chưa rõ, chỉ định rõ người ra quyết định thay vì tự ý điền giá trị ngầm định.</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I42" s="4" t="n">
@@ -2542,7 +2542,7 @@
       <c r="J42" s="3" t="n"/>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Người review cần tái tạo được lý do pass/fail và biết bản ghi nào cần xử lý.</t>
+          <t>Kết quả kiểm tra kỳ vọng dữ liệu (data expectation result) cần lưu trữ đầy đủ để phục vụ kiểm toán và xử lý lỗi: (a) Tên điều khoản/chiều chất lượng và phạm vi kiểm tra của lần chạy; (b) Giá trị quan sát được kèm mẫu số tính toán; (c) Ngưỡng chấp nhận và mức độ nghiêm trọng của lỗi; (d) Bằng chứng cụ thể về các dòng dữ liệu bị lỗi hoặc lát cắt dữ liệu vi phạm. Chỉ trả về giá trị boolean false là không đủ thông tin chẩn đoán.</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,3,4</t>
         </is>
       </c>
       <c r="I43" s="4" t="n">
@@ -2594,7 +2594,7 @@
       <c r="J43" s="3" t="n"/>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Liệt kê cả điều suite không quan sát.</t>
+          <t>Khi bộ kiểm tra đạt các tiêu chí not-null, type và range trên phân vùng của ngày hôm nay, các kết luận hợp lý là: (a) Toàn bộ các quy tắc đã triển khai đều đạt yêu cầu trên phạm vi phân vùng hôm nay; (c) Các phân vùng của những ngày khác vẫn chưa được kiểm tra; (d) Các quy tắc nghiệp vụ sâu hơn hoặc tính thẩm quyền của nguồn có thể chưa được kiểm tra trong bộ test này. Không thể suy diễn dữ liệu tương lai chắc chắn đúng hay độ chính xác bên ngoài đã được chứng minh.</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -2639,7 +2639,7 @@
       <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mẫu số là toàn bộ bản ghi mà rule đã chặn.</t>
+          <t>Độ chính xác (Precision) của quy tắc chặn lỗi: Tỷ lệ giữa số bản ghi thực sự bị lỗi (True Positives = 30) trên tổng số bản ghi mà quy tắc đã chặn (Total Predicted Positives = 40): Precision = 30 / 40 = 0,75 = 75%.</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -2729,7 +2729,7 @@
       <c r="J46" s="3" t="n"/>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Age bắt đầu ở source/effective time.</t>
+          <t>Độ tuổi của dữ liệu (data age) mà consumer quan sát được theo watermark: Tính từ mốc thời gian watermark an toàn (14:40) đến thời điểm hiện tại của hệ thống (15:10): 15:10 - 14:40 = 30 phút.</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I48" s="4" t="n">
@@ -2826,7 +2826,7 @@
       <c r="J48" s="3" t="n"/>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chọn signal có thể phản ánh parser làm rỗng/cắt/đổi language.</t>
+          <t>Khi số lượng dòng vẫn ổn định nhưng chất lượng câu trả lời bị suy giảm sau khi cập nhật bộ phân tích cú pháp (parser), các tín hiệu hữu ích để phát hiện sự cố dữ liệu gồm: (a) Tỷ lệ giá trị null theo từng trường dữ liệu; (b) Phân phối độ dài văn bản (text-length distribution) phát hiện hiện tượng bị cắt cụt; (c) Tỷ lệ phối hợp ngôn ngữ (language mix) phát hiện lỗi dịch/nhầm locale; (d) Số lượng giá trị phân biệt và độ hỗn loạn thông tin (cardinality/entropy) phát hiện lỗi trùng lặp/giảm đa dạng.</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4 → o5</t>
+          <t>o5 → o2 → o4 → o1 → o3</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -2923,7 +2923,7 @@
       <c r="J50" s="3" t="n"/>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Bắt đầu ở thứ agent nhìn thấy rồi lần producer của từng artifact.</t>
+          <t>Trình tự truy vết nguồn gốc dữ liệu ngược dòng (backwards data lineage) từ kết quả phục vụ agent về nguồn dữ liệu gốc: 1. Retrieved chunk mà agent trực tiếp quan sát thấy trong context (o5) -&gt; 2. Active index snapshot đang phục vụ truy vấn tại thời điểm đó (o2) -&gt; 3. Bản ghi chuẩn hóa (canonical record) trong kho lưu trữ (o4) -&gt; 4. Tác vụ và artifact chuyển đổi (transform run/artifact) tạo ra bản ghi đó (o1) -&gt; 5. Định danh và phiên bản dữ liệu nguồn ban đầu (source identity/version) (o3).</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I51" s="4" t="n">
@@ -2975,7 +2975,7 @@
       <c r="J51" s="3" t="n"/>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hỏi khi breach thì ai biết, ai làm gì và learner thấy gì.</t>
+          <t>Một thỏa thuận mức dịch vụ về độ tươi mới dữ liệu (freshness SLA) có tính hành động cao bắt buộc phải có: (a) Thời điểm phát sinh sự kiện kinh doanh tại nguồn để bắt đầu tính thời gian; (b) Ranh giới xuất bản dữ liệu phục vụ agent để kết thúc tính thời gian; (c) Ngưỡng thời gian và quy trình cảnh báo/leo thang khi vi phạm; (d) Người chịu trách nhiệm cụ thể và quy định hành vi xử lý khi dữ liệu bị cũ/quá hạn (stale-data policy).</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I56" s="4" t="n">
@@ -3219,7 +3219,7 @@
       <c r="J56" s="3" t="n"/>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Xét lúc source trễ, task giữa DAG fail và cần chạy lại một date range.</t>
+          <t>Để vận hành một pipeline dữ liệu tin cậy trong môi trường sản xuất, ngoài lịch chạy cron cần bổ sung các yêu cầu bắt buộc: (a) Đồ thị phụ thuộc dữ liệu và điều kiện sẵn sàng của dữ liệu nguồn (dependency graph / data sensors); (b) Chính sách thử lại riêng cho từng tác vụ kèm giới hạn tối đa; (c) Cơ chế cảnh báo vi phạm SLA, người sở hữu phụ trách và khả năng hiển thị trạng thái thực thi; (d) Các tham số chạy bù dữ liệu có chặn giới hạn (bounded backfill) và quản lý dấu vết dữ liệu (lineage).</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4 → o5</t>
+          <t>o2 → o1 → o3 → o4 → o5</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -3316,7 +3316,7 @@
       <c r="J58" s="3" t="n"/>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Không write trực tiếp vào alias đang serve.</t>
+          <t>Quy trình phát hành chỉ mục vector nguyên tử (atomic vector index publish) bảo đảm tính sẵn sàng: 1. Xây dựng bộ sưu tập staging độc lập (build staging collection) (o2) -&gt; 2. Xác minh số lượng bản ghi, schema, mẫu dữ liệu và manifest trên staging (o1) -&gt; 3. Chuyển đổi alias phục vụ sang bộ sưu tập staging một cách nguyên tử (switch serving alias atomically) (o3) -&gt; 4. Duy trì snapshot phiên bản phục vụ trước đó trong khoảng thời gian an toàn (o4) -&gt; 5. Rollback alias về snapshot cũ nếu các phép kiểm sau phát hành thất bại (o5).</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4 → o5</t>
+          <t>o5 → o2 → o4 → o1 → o3</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -3458,7 +3458,7 @@
       <c r="J61" s="3" t="n"/>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Xác định incident trước, rồi dùng signal rộng/rẻ trước targeted lineage.</t>
+          <t>Trình tự phân loại và xử lý sự cố dữ liệu (data incident triage) tối ưu chi phí và thời gian: 1. Ghi nhận triệu chứng sự cố, vi phạm SLA, phạm vi ảnh hưởng và giả thuyết ban đầu (o5) -&gt; 2. Kiểm tra độ tươi mới và mốc chạy thành công gần nhất (freshness/last success) (o2) -&gt; 3. Kiểm tra khối lượng dữ liệu và tỷ lệ lỗi theo từng giai đoạn đường ống (volume/stage errors) (o4) -&gt; 4. Kiểm tra các thay đổi về cấu trúc schema hoặc hợp đồng dữ liệu gần đây (o1) -&gt; 5. Truy vết ngược dòng lineage chi tiết về tận nguồn dữ liệu và người sở hữu phụ trách (o3).</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I62" s="4" t="n">
@@ -3510,7 +3510,7 @@
       <c r="J62" s="3" t="n"/>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Verify từ source tới bề mặt agent.</t>
+          <t>Bằng chứng kỹ thuật đầy đủ và thuyết phục để chính thức đóng một sự cố dữ liệu (data incident) bao gồm: (a) Bản ghi nguồn và bản ghi chuẩn hóa đã được xác minh đúng kèm đầy đủ lineage; (b) Các tín hiệu kiểm tra chất lượng dữ liệu liên quan đã vượt qua thành công; (c) Snapshot đang hoạt động ở tầng phục vụ mang đúng ID phiên bản đã khắc phục; (d) Truy vấn thực tế của người dùng ban đầu được chạy lại và trả về câu trả lời cùng trích dẫn nguồn hoàn toàn chính xác.</t>
         </is>
       </c>
     </row>
